--- a/task_1_3.xlsx
+++ b/task_1_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\math_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3766FB95-0E94-4D81-A048-E92A9C13C106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6EC3BA-4B6A-49FE-A0FE-99579AEA80D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3D11977B-6E7B-425F-AD88-162E10A9900B}"/>
   </bookViews>
@@ -237,7 +237,1225 @@
   </si>
   <si>
     <r>
-      <t>Нягт = масс / эзлэхүүн бол дээрх блокийн нягтын авч болох хамгийн бага утгыг ол.</t>
+      <t>Дугтуйны уртыг см-ээр тоймлоход 21 см байв. Дугтуйны урт хамгийн багадаа ямар байх вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 20 см  B. 20.5 см  C. 20.4 см  D. 21.0 см</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ил захидлын уртыг 0.1 нарийвчлалтай тоймлоход 20.5 см болжээ. Ил захидлын уртын хамгийн их утга?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 20.55 см  B. 20.54 см  C. 20.6 см  D. 21.0 см</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>20.5 см-ийн (0.1 нарийвчлалтай тоймлосон) ил захидал 21 см-ийн (см-ээр тоймлосон) дугтуйд багтах уу?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. Багтана  B. Багтахгүй  C. Заримдаа  D. Тодорхойгүй</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Хүний бие дунджаар $10^{14}$ ширхэг эсээс тогтдог. Нэг эс 1 нг жинтэй бол биеийн нийт эсийн массыг кг-аар илэрхийл.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 0.1 кг  B. 10 кг  C. 100 кг  D. 1 кг</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Дэлхийн масс ойролцоогоор $5.97 \times 10^{24}$ кг бол үүнийг тонн нэгжээр стандарт дүрсэд бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $5.97 \times 10^{21}$ т  B. $5.97 \times 10^{27}$ т  C. $5.97 \times 10^{18}$ т  D. $5.97 \times 10^{24}$ т</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Савангийн хөөсний зузаан $0.0000001$ м бол үүнийг 10-ын зэрэг оролцсон стандарт хэлбэрт бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $10^{-6}$ м  B. $10^{-7}$ м  C. $10^{-8}$ м  D. $1 \times 10^7$ м</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Нарны гэрэл дэлхий рүү 8 минутад ирдэг. Гэрлийн хурд $3 \times 10^8$ м/с бол нарнаас дэлхий хүртэлх зайг км-ээр илэрхийл.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 144 сая км  B. 150 сая км  C. 1.44 сая км  D. 15 сая км</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Австралийн газар нутаг 7,692,024 км$^2$, Коста-Рика 51,100 км$^2$. Австрали Коста-Рикагаас ойролцоогоор хэд дахин их вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 100 дахин  B. 154 дахин  C. 21 дахин  D. 150 дахин</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$1.5$ см ирмэгтэй жижиг куб ба 5 см ирмэгтэй том кубийн эзлэхүүнүүдийн харьцааг бүхлээр тоймло.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 3 дахин  B. 37 дахин  C. 10 дахин  D. 25 дахин</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Од эрхэс дэлхийгээс 500 гэрлийн жилийн зайд оршдог. Энэ зайг км-ээр илэрхийлж стандарт дүрсэд бич ($1$ г.ж $\approx 9.46 \times 10^{12}$ км).</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $4.73 \times 10^{15}$ км  B. $47.3 \times 10^{14}$ км  C. $4.73 \times 10^{12}$ км  D. $9.46 \times 10^{14}$ км</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Бичгийн цаасны зузаан $0.0000213$ м бол үүнийг мм нэгжээр стандарт дүрсэд бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $2.13 \times 10^{-2}$ мм  B. $21.3 \times 10^{-3}$ мм  C. $0.213$ мм  D. $2.13 \times 10^{-5}$ мм</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Билгүүн нэг тоог 2.6 гэж (0.1 нарийвчлалтай), Марал 2.639 гэж тоймложээ. Уг тоо 2.6387 байх боломжтой юу?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. Боломжтой  B. Боломжгүй  C. Маралынх буруу  D. Билгүүнийх буруу</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Кубийн эзлэхүүнийг Билгүүн 3.7, Марал 3.75 гэж тоймлосон нь хоёул зөв бол эзлэхүүний авч болох хамгийн бага утга?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 3.745  B. 3.70  C. 3.65  D. 3.74</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Цаасны массыг 1 мг-аар илэрхийлэхдээ 10-ын зэрэг ашиглавал хэдэн кг болох вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $10^{-3}$ кг  B. $10^{-6}$ кг  C. $10^6$ кг  D. $10^{-9}$ кг</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Дэлхийн экваторын радиус 6378.1 км бол үүнийг метрээр илэрхийлж стандарт дүрсэд бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $6.3781 \times 10^6$ м  B. $6.3781 \times 10^3$ м  C. $63.781 \times 10^5$ м  D. $6.3781 \times 10^7$ м</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Нэхмэлчид хивс нэхэхдээ урт нь 36 см, өргөн нь 28 см байх хээ үүсгэв. Тэгш хэмтэй хээний хамгийн бага хэмжээ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 120 см  B. 4 см  C. 92.2 см  D. 252 см</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Усан сангийн урт 10.3 м, өргөн 6.2 м, өндөр 3.7 м бол эзлэхүүнийг 0.1 нарийвчлалтай тоймло.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 236.3 м$^3$  B. 236.1 м$^3$  C. 236.0 м$^3$  D. 236.08 м$^3$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Гэрлийн жил нь $946,100,000,000,000,000$ м бол үүнийг стандарт дүрсээр бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $9.461 \times 10^{17}$ м  B. $9.461 \times 10^{12}$ м  C. $9.461 \times 10^{15}$ м  D. $0.946 \times 10^{18}$ м</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Хөлийн хумс цагт $0.000,000,000,007,323$ м ургадаг бол мм-ээр стандарт дүрсээр бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $7.323 \times 10^{-9}$ мм  B. $7.323 \times 10^{-12}$ мм  C. $7.323 \times 10^{-8}$ мм  D. $0.732 \times 10^{-9}$ мм</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Бумба хэлбэртэй савны радиусыг дециметрээр тоймлоход 16 дм болжээ. Эзлэхүүний авч болох хамгийн их утга?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 17157 дм$^3$  B. 22438 дм$^3$  C. 18807 дм$^3$  D. 20000 дм$^3$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Радиус нь 16 дм (тоймлосон) бумбын эзлэхүүний хамгийн бага утга?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 15591 дм$^3$  B. 16000 дм$^3$  C. 14000 дм$^3$  D. 18807 дм$^3$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Тэгш өнцөгт параллелепипедийн талууд 1, $\sqrt{3}, \sqrt{5}$ бол эзлэхүүнийг 0.1-ээр тоймло.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 3.8  B. 3.9  C. 4.0  D. 3.3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Эверестийн оргил 29029 тохой бол $x \times 10^y$ хэлбэрт (x, y - нэг оронтой) бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $2.9 \times 10^4$  B. $3 \times 10^4$  C. $29 \times 10^3$  D. $0.3 \times 10^5$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Машины дугуй 0.6 м диаметртэй. 1 км явахад дугуй хэдэн удаа эргэх вэ? (Бүхлээр тоймло)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 530  B. 531  C. 500  D. 600</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">650 мл-ийн 15% хэдэн мл болох вэ? </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A. 9.75 мл  B. 97.5 мл  C. 975 мл  D. 0.975 мл</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Цилиндр савны өндөр 65 см, диаметр 40 см. 1 литр элс 2 кг жинтэй бол саванд хэдэн кг элс орох вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 150 кг  B. 163.28 кг  C. 160 кг  D. 170 кг</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Төсөөтэй хоёр биетийн талбайн харьцаа $k^2=4$ бол ирмэгийн харьцаа хэд вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 2  B. 4  C. 8  D. 16</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Төсөөтэй биетийн эзлэхүүний харьцаа $k^3=27$ бол гадаргуугийн талбайн харьцаа?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 3  B. 9  C. 27  D. 81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Төсөөтэй биетийн эзлэхүүний харьцаа $k^3=125$ бол ирмэгийн харьцаа?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 5  B. 25  C. 10  D. 50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Угаалгын шингэн 650 мл ба 25% нэмэгдэлтэй бол ердийн савны хэмжээ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 500 мл  B. 520 мл  C. 480 мл  D. 600 мл</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Гар чийдэнгийн зай 12 цаг ажилладаг ба 30 мин нэмэгдсэн бол хэдэн хувиар өссөн бэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 4%  B. 4.17%  C. 5%  D. 10%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Хуурай мөөгөнд 12% ус, шинэ мөөгөнд 90% ус байдаг. 22 кг шинэ мөөгнөөс хэдэн кг хуурай мөөг авах вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 2.2 кг  B. 2.5 кг  C. 3 кг  D. 1.8 кг</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1 литр 6%-ийн спиртээс 5% болгоход хэдэн литр 3%-ийн спирт нэмэх вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 0.5 л  B. 1 л  C. 0.2 л  D. 0.8 л</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$2^{3x} = 64$ бол $x$-ийг ол.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 40A. 1  B. 2  C. 3  D. 4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$8^{x+1} = 4$ хялбар илтгэгч тэгшитгэлийг бод.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. -1/3  B. 1/3  C. 3  D. 5/3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$27^x = 9$ илтгэгч тэгшитгэлийн шийд?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 2/3  B. 3/2  C. 1/2  D. 1/3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$100 \div 10^{-3}$ үйлдлийн хариуг 10-ын зэргээр илэрхийл.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $10^5$  B. $10^2$  C. $10^{-1}$  D. $10^1$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Нарны масс ойролцоогоор $1.98 \times 10^{30}$ кг байдаг. Үүнийг аравтын бутархайгаар бичвэл 8-ын цифрийн ард хэдэн тэг бичигдэх вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 30  B. 29  C. 28  D. 31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Андромед галактик хүртэлх зай ойролцоогоор $2 \times 10^{19}$ км. Үүнийг гэрлийн жилээр илэрхийл ($1$ г.ж $\approx 9.46 \times 10^{12}$ км).</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 2.1 сая г.ж  B. 1.5 сая г.ж  C. 3 сая г.ж  D. 0.5 сая г.ж</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Монгол улсын газар нутаг 1,564,116 км$^2$ бол үүнийг стандарт дүрсэд бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $1.564116 \times 10^6$  B. $15.6 \times 10^5$  C. $1.5 \times 10^6$  D. $156.4 \times 10^4$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Хүний өндөгөн эс ойролцоогоор 1 нг (нанограмм) жинтэй. Үүнийг кг нэгжээр стандарт дүрсэд бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $10^{-9}$ кг  B. $10^{-12}$ кг  C. $10^{-6}$ кг  D. $10^{-15}$ кг</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Бичил биетний урт 3.6 $\mu$г (микрограмм). Үүнийг кг нэгжээр стандарт дүрсэд бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $3.6 \times 10^{-6}$ кг  B. $3.6 \times 10^{-9}$ кг  C. $3.6 \times 10^{-12}$ кг  D. $3.6 \times 10^9$ кг</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Дэлхийн экваторын бүс 40075.012 км бол үүнийг 0.1 нарийвчлалтай тоймло.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 40075.0  B. 40075.1  C. 40075  D. 40080</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$16 \times 10^7$ тоо нь $4 \times 10^3$ тооноос хэд дахин их вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $4 \times 10^4$  B. $4 \times 10^{10}$  C. 4000  D. 400</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Инженерүүд салхин сэнсний цамхгийг барихад нэг цамхагт 3.2 сая доллар зарцуулдаг. 3 цамхаг барих зардлыг стандарт дүрсээр бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $9.6 \times 10^5$  B. $9.6 \times 10^6$  C. $0.96 \times 10^7$  D. $96 \times 10^6$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Салхин сэнсний засвар үйлчилгээний зардал жилд 400,000 доллар. Үүнийг 10-ын зэрэг ашиглан бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $4 \times 10^4$  B. $4 \times 10^5$  C. $0.4 \times 10^6$  D. $40 \times 10^4$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Тэгш өнцөгт талбайн урт 13 см, өргөн 8 см (см-ээр тоймлосон). Талбайн авч болох хамгийн их утга?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 104 см$^2$  B. 114.75 см$^2$  C. 108.25 см$^2$  D. 110 см$^2$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Бархасбадь гараг нарнаас 778 сая км зайд оршдог. Гэрэл (хурд $3 \times 10^5$ км/с) Бархасбадь хүртэл хэдэн секундэд очих вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 2593 сек  B. 2334 сек  C. 1500 сек  D. 3000 сек</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Хайрцагны өндөр 4 см, гадаргуугийн талбай нь 96 см$^2$. Төсөөтэй том хайрцагны талбай 864 см$^2$ бол том хайрцагны өндөр?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 8 см  B. 12 см  C. 16 см  D. 24 см</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Жижиг хайрцагны эзлэхүүн 64 см$^3$, том хайрцагны талбайн харьцаа $k^2=9$ бол том хайрцагны эзлэхүүн?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 192 см$^3$  B. 576 см$^3$  C. 1728 см$^3$  D. 512 см$^3$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Савангийн хөөсний зузаан $0.0000001$ м бол үүнийг $1 \times 10^n$ дүрсэд бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $n = -6$  B. $n = -7$  C. $n = -8$  D. $n = 7$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Хүний биеийн эсийн масс 100 кг ба нэг эс 1 нг бол нийт эсийн тоог стандарт дүрсээр бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $1 \times 10^{11}$  B. $1 \times 10^{14}$  C. $1 \times 10^{15}$  D. $1 \times 10^{12}$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Австралийн газар нутаг ойролцоогоор 7.7 сая км$^2$, Коста Рика 51 мянган км$^2$. Австрали хэд дахин их вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 100 дахин  B. 150 дахин  C. 200 дахин  D. 50 дахин</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Квадратын тал $\sqrt{50}$ см бол түүний талыг 0.1 нарийвчлалтай тоймло.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 7.0 см  B. 7.1 см  C. 7.07 см  D. 7.2 см</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Од хүртэлх зай 500 гэрлийн жил бол км-ээр илэрхийлж 2 тэмдэгтээр тоймло ($1$ г.ж $\approx 9.5 \times 10^{12}$ км).</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $4.8 \times 10^{15}$ км  B. $4.7 \times 10^{15}$ км  C. $5.0 \times 10^{14}$ км  D. $9.5 \times 10^{14}$ км</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$325.78$ тоог 3 тэмдэгтээр тоймло.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 54, 55A. 326  B. 325  C. 330  D. 325.8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$95 \times 212$ үржвэрийг тоог тоймлох замаар багцаалж ол.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 18,000  B. 20,000  C. 21,000  D. 19,000</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$77.9 \times 22.6$ үйлдлийг тоймлож гүйцэтгэхэд гарах багцаа утга?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 1600  B. 1760  C. 1800  D. 1500</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Радиус нь 16 дм (тоймлосон) бөмбөрцгийн эзлэхүүний дээд хязгаар?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 18807 дм$^3$  B. 22438 дм$^3$  C. 20000 дм$^3$  D. 21000 дм$^3$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Гэрийн шалны радиус 3 м (тоймлосон). Талбайн авч болох дээд утга ($S=\pi r^2$)?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 28.26 м$^2$  B. 38.465 м$^2$  C. 30.0 м$^2$  D. 35.5 м$^2$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Гурилын жинг 0.5 нарийвчлалтай тоймлоход 169.5 кг болсон бол хамгийн бага жин?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 169.25 кг  B. 169.0 кг  C. 169.4 кг  D. 169.45 кг</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$59,588$ тоог нэг тэмдэгтээр тоймло.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 60,000  B. 50,000  C. 59,000  D. 6,000</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$3.9 \times 10^8 \times 2.6 \times 10^{-5}$ үржвэрийг стандарт дүрсэд бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $1.014 \times 10^4$  B. $10.14 \times 10^3$  C. $1.014 \times 10^3$  D. $1.0 \times 10^4$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$0.00000089$ тоог стандарт дүрсэд бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $8.9 \times 10^{-7}$  B. $8.9 \times 10^{-6}$  C. $0.89 \times 10^{-6}$  D. $8.9 \times 10^{-8}$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>15 их наяд тоог стандарт дүрсэд бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $1.5 \times 10^{12}$  B. $1.5 \times 10^{13}$  C. $15 \times 10^{12}$  D. $1.5 \times 10^{11}$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1 нг (нанограмм)-ийг кг-аар илэрхийл.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $10^{-9}$ кг  B. $10^{-12}$ кг  C. $10^{-6}$ кг  D. $10^{-10}$ кг</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3.6 $\mu$г (микрограмм)-ийг кг-аар илэрхийл.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $3.6 \times 10^{-9}$ кг  B. $3.6 \times 10^{-6}$ кг  C. $3.6 \times 10^{-12}$ кг  D. $3.6 \times 10^{-10}$ кг</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Хөлөг онгоц дарвуул ашиглан жилд 3.5 сая литр түлш хэрэглэдэг. Дарвуул 20% хэмнэдэг бол хэдэн литр түлш хэмнэх вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7, 62A. 700,000 л  B. 500,000 л  C. 800,000 л  D. 1,000,000 л</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Түлшний үнэ 0.42 Z/литр бол жилд хэмнэх 700,000 литр түлшний үнийг ол.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 294,000 Z  B. 300,000 Z  C. 250,000 Z  D. 350,000 Z</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Салхин сэнсний далавчны урт 40 м. Аюулгүй зай нь далавчны уртаас 5 дахин их бол энэ зай хэд вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 160 м  B. 200 м  C. 250 м  D. 300 м</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Хоёр цамхгийн хоорондох зай 177 м бол аюулгүй байдлын 200 м-ийн дүрмийг хангасан уу?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. Хангасан  B. Хангаагүй  C. Тэнцүү  D. Мэдэх боломжгүй</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Салхин сэнс барихад 2.5 сая доллар зарцуулсан. Жилд 294,000 доллар хэмнэдэг бол хэдэн жилийн дараа зардлаа нөхөх вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 5-6 жил  B. 8-9 жил  C. 10 жил  D. 12 жил</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Сэнсний дээд хурд 300 км/ц бол үүнийг м/с нэгжид шилжүүлж бүхлээр тоймло.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 8A. 83 м/с  B. 100 м/с  C. 50 м/с  D. 120 м/с</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Хурдны нэгжийг шилжүүл: 150 м/с хэдэн км/ц болох вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 450 км/ц  B. 540 км/ц  C. 300 км/ц  D. 600 км/ц</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Хурдны нэгжийг шилжүүл: 300 м/с хэдэн км/ц болох вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 1000 км/ц  B. 1080 км/ц  C. 900 км/ц  D. 1200 км/ц</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Төсөөтэй хоёр дүрсийн талбайн харьцаа $k^2 = 4/121$ бол ирмэгийн харьцаа?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 2/11  B. 4/11  C. 2/121  D. 16/121</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>65.1359 тоог 0.01 нарийвчлалтай тоймло.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 65.13  B. 65.14  C. 65.1  D. 65.136</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0.00025648 тоог 2 тэмдэгтээр тоймло.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 0.00025  B. 0.00026  C. 0.0003  D. 0.000256</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Усан сангийн эзлэхүүн 236.082 м$^3$ бол 5 тэмдэгтээр тоймло.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 236.08  B. 236.1  C. 236.09  D. 236.00</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Гурвалжны талууд 9, 12, 15 бол түүний талбайг ол.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 54  B. 90  C. 108  D. 45</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Тэгш өнцөгтийн талууд 5 см ба 12 см бол диагоналийн уртыг ол.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 66A. 13 см  B. 15 см  C. 17 см  D. 14 см</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Кубийн ирмэг 4 см бол түүний диагональ огтлолын талбай?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $16\sqrt{2}$ см$^2$  B. 16 см$^2$  C. $16\sqrt{3}$ см$^2$  D. 32 см$^2$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10%-ийн 150 г уусмал дээр 5%-ийн 60 г уусмал нэмэхэд концентраци хэд болох вэ?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 8.57%  B. 9%  C. 7.5%  D. 8%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Буудлагын тамирчин байг онох магадлал 0.6 ба 0.7 бол хоёулаа онохгүй байх магадлал?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 0.12  B. 0.42  C. 0.13  D. 0.18</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Гэрлийн хурд $3 \times 10^8$ м/с-ийг км/с нэгжид шилжүүл.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. 300,000 км/с  B. 3,000,000 км/с  C. 30,000 км/с  D. 3,000 км/с</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$0.019 \times 10^{-8}$ тоог стандарт дүрсэд бич.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $1.9 \times 10^{-10}$  B. $1.9 \times 10^{-9}$  C. $19 \times 10^{-10}$  D. $1.9 \times 10^{-7}$</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Дэлхийн экваторын радиус 6378.1 км бол үүнийг стандарт дүрсээр метрээр илэрхийл.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> A. $6.3781 \times 10^6$ м  B. $63.781 \times 10^5$ м  C. $6.3 \times 10^6$ м  D. $6.3781 \times 10^3$ м</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>$Нягт = масс / эзлэхүүн$ бол дээрх блокийн нягтын авч болох хамгийн бага утгыг ол.</t>
     </r>
     <r>
       <rPr>
@@ -247,1224 +1465,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> A. 4.3  B. 4.6  C. 5.0  D. 5.7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Дугтуйны уртыг см-ээр тоймлоход 21 см байв. Дугтуйны урт хамгийн багадаа ямар байх вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 20 см  B. 20.5 см  C. 20.4 см  D. 21.0 см</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Ил захидлын уртыг 0.1 нарийвчлалтай тоймлоход 20.5 см болжээ. Ил захидлын уртын хамгийн их утга?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 20.55 см  B. 20.54 см  C. 20.6 см  D. 21.0 см</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>20.5 см-ийн (0.1 нарийвчлалтай тоймлосон) ил захидал 21 см-ийн (см-ээр тоймлосон) дугтуйд багтах уу?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. Багтана  B. Багтахгүй  C. Заримдаа  D. Тодорхойгүй</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хүний бие дунджаар $10^{14}$ ширхэг эсээс тогтдог. Нэг эс 1 нг жинтэй бол биеийн нийт эсийн массыг кг-аар илэрхийл.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 0.1 кг  B. 10 кг  C. 100 кг  D. 1 кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Дэлхийн масс ойролцоогоор $5.97 \times 10^{24}$ кг бол үүнийг тонн нэгжээр стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $5.97 \times 10^{21}$ т  B. $5.97 \times 10^{27}$ т  C. $5.97 \times 10^{18}$ т  D. $5.97 \times 10^{24}$ т</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Савангийн хөөсний зузаан $0.0000001$ м бол үүнийг 10-ын зэрэг оролцсон стандарт хэлбэрт бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $10^{-6}$ м  B. $10^{-7}$ м  C. $10^{-8}$ м  D. $1 \times 10^7$ м</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Нарны гэрэл дэлхий рүү 8 минутад ирдэг. Гэрлийн хурд $3 \times 10^8$ м/с бол нарнаас дэлхий хүртэлх зайг км-ээр илэрхийл.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 144 сая км  B. 150 сая км  C. 1.44 сая км  D. 15 сая км</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Австралийн газар нутаг 7,692,024 км$^2$, Коста-Рика 51,100 км$^2$. Австрали Коста-Рикагаас ойролцоогоор хэд дахин их вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 100 дахин  B. 154 дахин  C. 21 дахин  D. 150 дахин</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$1.5$ см ирмэгтэй жижиг куб ба 5 см ирмэгтэй том кубийн эзлэхүүнүүдийн харьцааг бүхлээр тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 3 дахин  B. 37 дахин  C. 10 дахин  D. 25 дахин</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Од эрхэс дэлхийгээс 500 гэрлийн жилийн зайд оршдог. Энэ зайг км-ээр илэрхийлж стандарт дүрсэд бич ($1$ г.ж $\approx 9.46 \times 10^{12}$ км).</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $4.73 \times 10^{15}$ км  B. $47.3 \times 10^{14}$ км  C. $4.73 \times 10^{12}$ км  D. $9.46 \times 10^{14}$ км</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Бичгийн цаасны зузаан $0.0000213$ м бол үүнийг мм нэгжээр стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $2.13 \times 10^{-2}$ мм  B. $21.3 \times 10^{-3}$ мм  C. $0.213$ мм  D. $2.13 \times 10^{-5}$ мм</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Билгүүн нэг тоог 2.6 гэж (0.1 нарийвчлалтай), Марал 2.639 гэж тоймложээ. Уг тоо 2.6387 байх боломжтой юу?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. Боломжтой  B. Боломжгүй  C. Маралынх буруу  D. Билгүүнийх буруу</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Кубийн эзлэхүүнийг Билгүүн 3.7, Марал 3.75 гэж тоймлосон нь хоёул зөв бол эзлэхүүний авч болох хамгийн бага утга?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 3.745  B. 3.70  C. 3.65  D. 3.74</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Цаасны массыг 1 мг-аар илэрхийлэхдээ 10-ын зэрэг ашиглавал хэдэн кг болох вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $10^{-3}$ кг  B. $10^{-6}$ кг  C. $10^6$ кг  D. $10^{-9}$ кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Дэлхийн экваторын радиус 6378.1 км бол үүнийг метрээр илэрхийлж стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $6.3781 \times 10^6$ м  B. $6.3781 \times 10^3$ м  C. $63.781 \times 10^5$ м  D. $6.3781 \times 10^7$ м</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Нэхмэлчид хивс нэхэхдээ урт нь 36 см, өргөн нь 28 см байх хээ үүсгэв. Тэгш хэмтэй хээний хамгийн бага хэмжээ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 120 см  B. 4 см  C. 92.2 см  D. 252 см</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Усан сангийн урт 10.3 м, өргөн 6.2 м, өндөр 3.7 м бол эзлэхүүнийг 0.1 нарийвчлалтай тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 236.3 м$^3$  B. 236.1 м$^3$  C. 236.0 м$^3$  D. 236.08 м$^3$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Гэрлийн жил нь $946,100,000,000,000,000$ м бол үүнийг стандарт дүрсээр бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $9.461 \times 10^{17}$ м  B. $9.461 \times 10^{12}$ м  C. $9.461 \times 10^{15}$ м  D. $0.946 \times 10^{18}$ м</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хөлийн хумс цагт $0.000,000,000,007,323$ м ургадаг бол мм-ээр стандарт дүрсээр бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $7.323 \times 10^{-9}$ мм  B. $7.323 \times 10^{-12}$ мм  C. $7.323 \times 10^{-8}$ мм  D. $0.732 \times 10^{-9}$ мм</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Бумба хэлбэртэй савны радиусыг дециметрээр тоймлоход 16 дм болжээ. Эзлэхүүний авч болох хамгийн их утга?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 17157 дм$^3$  B. 22438 дм$^3$  C. 18807 дм$^3$  D. 20000 дм$^3$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Радиус нь 16 дм (тоймлосон) бумбын эзлэхүүний хамгийн бага утга?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 15591 дм$^3$  B. 16000 дм$^3$  C. 14000 дм$^3$  D. 18807 дм$^3$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Тэгш өнцөгт параллелепипедийн талууд 1, $\sqrt{3}, \sqrt{5}$ бол эзлэхүүнийг 0.1-ээр тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 3.8  B. 3.9  C. 4.0  D. 3.3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Эверестийн оргил 29029 тохой бол $x \times 10^y$ хэлбэрт (x, y - нэг оронтой) бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $2.9 \times 10^4$  B. $3 \times 10^4$  C. $29 \times 10^3$  D. $0.3 \times 10^5$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Машины дугуй 0.6 м диаметртэй. 1 км явахад дугуй хэдэн удаа эргэх вэ? (Бүхлээр тоймло)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 530  B. 531  C. 500  D. 600</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">650 мл-ийн 15% хэдэн мл болох вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 9.75 мл  B. 97.5 мл  C. 975 мл  D. 0.975 мл</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Цилиндр савны өндөр 65 см, диаметр 40 см. 1 литр элс 2 кг жинтэй бол саванд хэдэн кг элс орох вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 150 кг  B. 163.28 кг  C. 160 кг  D. 170 кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Төсөөтэй хоёр биетийн талбайн харьцаа $k^2=4$ бол ирмэгийн харьцаа хэд вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 2  B. 4  C. 8  D. 16</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Төсөөтэй биетийн эзлэхүүний харьцаа $k^3=27$ бол гадаргуугийн талбайн харьцаа?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 3  B. 9  C. 27  D. 81</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Төсөөтэй биетийн эзлэхүүний харьцаа $k^3=125$ бол ирмэгийн харьцаа?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 5  B. 25  C. 10  D. 50</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Угаалгын шингэн 650 мл ба 25% нэмэгдэлтэй бол ердийн савны хэмжээ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 500 мл  B. 520 мл  C. 480 мл  D. 600 мл</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Гар чийдэнгийн зай 12 цаг ажилладаг ба 30 мин нэмэгдсэн бол хэдэн хувиар өссөн бэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 4%  B. 4.17%  C. 5%  D. 10%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хуурай мөөгөнд 12% ус, шинэ мөөгөнд 90% ус байдаг. 22 кг шинэ мөөгнөөс хэдэн кг хуурай мөөг авах вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 2.2 кг  B. 2.5 кг  C. 3 кг  D. 1.8 кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1 литр 6%-ийн спиртээс 5% болгоход хэдэн литр 3%-ийн спирт нэмэх вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 0.5 л  B. 1 л  C. 0.2 л  D. 0.8 л</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$2^{3x} = 64$ бол $x$-ийг ол.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 40A. 1  B. 2  C. 3  D. 4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$8^{x+1} = 4$ хялбар илтгэгч тэгшитгэлийг бод.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. -1/3  B. 1/3  C. 3  D. 5/3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$27^x = 9$ илтгэгч тэгшитгэлийн шийд?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 2/3  B. 3/2  C. 1/2  D. 1/3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$100 \div 10^{-3}$ үйлдлийн хариуг 10-ын зэргээр илэрхийл.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $10^5$  B. $10^2$  C. $10^{-1}$  D. $10^1$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Нарны масс ойролцоогоор $1.98 \times 10^{30}$ кг байдаг. Үүнийг аравтын бутархайгаар бичвэл 8-ын цифрийн ард хэдэн тэг бичигдэх вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 30  B. 29  C. 28  D. 31</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Андромед галактик хүртэлх зай ойролцоогоор $2 \times 10^{19}$ км. Үүнийг гэрлийн жилээр илэрхийл ($1$ г.ж $\approx 9.46 \times 10^{12}$ км).</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 2.1 сая г.ж  B. 1.5 сая г.ж  C. 3 сая г.ж  D. 0.5 сая г.ж</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Монгол улсын газар нутаг 1,564,116 км$^2$ бол үүнийг стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $1.564116 \times 10^6$  B. $15.6 \times 10^5$  C. $1.5 \times 10^6$  D. $156.4 \times 10^4$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хүний өндөгөн эс ойролцоогоор 1 нг (нанограмм) жинтэй. Үүнийг кг нэгжээр стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $10^{-9}$ кг  B. $10^{-12}$ кг  C. $10^{-6}$ кг  D. $10^{-15}$ кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Бичил биетний урт 3.6 $\mu$г (микрограмм). Үүнийг кг нэгжээр стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $3.6 \times 10^{-6}$ кг  B. $3.6 \times 10^{-9}$ кг  C. $3.6 \times 10^{-12}$ кг  D. $3.6 \times 10^9$ кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Дэлхийн экваторын бүс 40075.012 км бол үүнийг 0.1 нарийвчлалтай тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 40075.0  B. 40075.1  C. 40075  D. 40080</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$16 \times 10^7$ тоо нь $4 \times 10^3$ тооноос хэд дахин их вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $4 \times 10^4$  B. $4 \times 10^{10}$  C. 4000  D. 400</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Инженерүүд салхин сэнсний цамхгийг барихад нэг цамхагт 3.2 сая доллар зарцуулдаг. 3 цамхаг барих зардлыг стандарт дүрсээр бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $9.6 \times 10^5$  B. $9.6 \times 10^6$  C. $0.96 \times 10^7$  D. $96 \times 10^6$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Салхин сэнсний засвар үйлчилгээний зардал жилд 400,000 доллар. Үүнийг 10-ын зэрэг ашиглан бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $4 \times 10^4$  B. $4 \times 10^5$  C. $0.4 \times 10^6$  D. $40 \times 10^4$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Тэгш өнцөгт талбайн урт 13 см, өргөн 8 см (см-ээр тоймлосон). Талбайн авч болох хамгийн их утга?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 104 см$^2$  B. 114.75 см$^2$  C. 108.25 см$^2$  D. 110 см$^2$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Бархасбадь гараг нарнаас 778 сая км зайд оршдог. Гэрэл (хурд $3 \times 10^5$ км/с) Бархасбадь хүртэл хэдэн секундэд очих вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 2593 сек  B. 2334 сек  C. 1500 сек  D. 3000 сек</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хайрцагны өндөр 4 см, гадаргуугийн талбай нь 96 см$^2$. Төсөөтэй том хайрцагны талбай 864 см$^2$ бол том хайрцагны өндөр?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 8 см  B. 12 см  C. 16 см  D. 24 см</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Жижиг хайрцагны эзлэхүүн 64 см$^3$, том хайрцагны талбайн харьцаа $k^2=9$ бол том хайрцагны эзлэхүүн?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 192 см$^3$  B. 576 см$^3$  C. 1728 см$^3$  D. 512 см$^3$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Савангийн хөөсний зузаан $0.0000001$ м бол үүнийг $1 \times 10^n$ дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $n = -6$  B. $n = -7$  C. $n = -8$  D. $n = 7$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хүний биеийн эсийн масс 100 кг ба нэг эс 1 нг бол нийт эсийн тоог стандарт дүрсээр бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $1 \times 10^{11}$  B. $1 \times 10^{14}$  C. $1 \times 10^{15}$  D. $1 \times 10^{12}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Австралийн газар нутаг ойролцоогоор 7.7 сая км$^2$, Коста Рика 51 мянган км$^2$. Австрали хэд дахин их вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 100 дахин  B. 150 дахин  C. 200 дахин  D. 50 дахин</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Квадратын тал $\sqrt{50}$ см бол түүний талыг 0.1 нарийвчлалтай тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 7.0 см  B. 7.1 см  C. 7.07 см  D. 7.2 см</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Од хүртэлх зай 500 гэрлийн жил бол км-ээр илэрхийлж 2 тэмдэгтээр тоймло ($1$ г.ж $\approx 9.5 \times 10^{12}$ км).</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $4.8 \times 10^{15}$ км  B. $4.7 \times 10^{15}$ км  C. $5.0 \times 10^{14}$ км  D. $9.5 \times 10^{14}$ км</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$325.78$ тоог 3 тэмдэгтээр тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 54, 55A. 326  B. 325  C. 330  D. 325.8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$95 \times 212$ үржвэрийг тоог тоймлох замаар багцаалж ол.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 18,000  B. 20,000  C. 21,000  D. 19,000</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$77.9 \times 22.6$ үйлдлийг тоймлож гүйцэтгэхэд гарах багцаа утга?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 1600  B. 1760  C. 1800  D. 1500</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Радиус нь 16 дм (тоймлосон) бөмбөрцгийн эзлэхүүний дээд хязгаар?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 18807 дм$^3$  B. 22438 дм$^3$  C. 20000 дм$^3$  D. 21000 дм$^3$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Гэрийн шалны радиус 3 м (тоймлосон). Талбайн авч болох дээд утга ($S=\pi r^2$)?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 28.26 м$^2$  B. 38.465 м$^2$  C. 30.0 м$^2$  D. 35.5 м$^2$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Гурилын жинг 0.5 нарийвчлалтай тоймлоход 169.5 кг болсон бол хамгийн бага жин?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 169.25 кг  B. 169.0 кг  C. 169.4 кг  D. 169.45 кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$59,588$ тоог нэг тэмдэгтээр тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 60,000  B. 50,000  C. 59,000  D. 6,000</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$3.9 \times 10^8 \times 2.6 \times 10^{-5}$ үржвэрийг стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $1.014 \times 10^4$  B. $10.14 \times 10^3$  C. $1.014 \times 10^3$  D. $1.0 \times 10^4$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$0.00000089$ тоог стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $8.9 \times 10^{-7}$  B. $8.9 \times 10^{-6}$  C. $0.89 \times 10^{-6}$  D. $8.9 \times 10^{-8}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>15 их наяд тоог стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $1.5 \times 10^{12}$  B. $1.5 \times 10^{13}$  C. $15 \times 10^{12}$  D. $1.5 \times 10^{11}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1 нг (нанограмм)-ийг кг-аар илэрхийл.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $10^{-9}$ кг  B. $10^{-12}$ кг  C. $10^{-6}$ кг  D. $10^{-10}$ кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3.6 $\mu$г (микрограмм)-ийг кг-аар илэрхийл.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $3.6 \times 10^{-9}$ кг  B. $3.6 \times 10^{-6}$ кг  C. $3.6 \times 10^{-12}$ кг  D. $3.6 \times 10^{-10}$ кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хөлөг онгоц дарвуул ашиглан жилд 3.5 сая литр түлш хэрэглэдэг. Дарвуул 20% хэмнэдэг бол хэдэн литр түлш хэмнэх вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 7, 62A. 700,000 л  B. 500,000 л  C. 800,000 л  D. 1,000,000 л</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Түлшний үнэ 0.42 Z/литр бол жилд хэмнэх 700,000 литр түлшний үнийг ол.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 294,000 Z  B. 300,000 Z  C. 250,000 Z  D. 350,000 Z</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Салхин сэнсний далавчны урт 40 м. Аюулгүй зай нь далавчны уртаас 5 дахин их бол энэ зай хэд вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 160 м  B. 200 м  C. 250 м  D. 300 м</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хоёр цамхгийн хоорондох зай 177 м бол аюулгүй байдлын 200 м-ийн дүрмийг хангасан уу?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. Хангасан  B. Хангаагүй  C. Тэнцүү  D. Мэдэх боломжгүй</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Салхин сэнс барихад 2.5 сая доллар зарцуулсан. Жилд 294,000 доллар хэмнэдэг бол хэдэн жилийн дараа зардлаа нөхөх вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 5-6 жил  B. 8-9 жил  C. 10 жил  D. 12 жил</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Сэнсний дээд хурд 300 км/ц бол үүнийг м/с нэгжид шилжүүлж бүхлээр тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 8A. 83 м/с  B. 100 м/с  C. 50 м/с  D. 120 м/с</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хурдны нэгжийг шилжүүл: 150 м/с хэдэн км/ц болох вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 450 км/ц  B. 540 км/ц  C. 300 км/ц  D. 600 км/ц</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хурдны нэгжийг шилжүүл: 300 м/с хэдэн км/ц болох вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 1000 км/ц  B. 1080 км/ц  C. 900 км/ц  D. 1200 км/ц</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Төсөөтэй хоёр дүрсийн талбайн харьцаа $k^2 = 4/121$ бол ирмэгийн харьцаа?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 2/11  B. 4/11  C. 2/121  D. 16/121</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>65.1359 тоог 0.01 нарийвчлалтай тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 65.13  B. 65.14  C. 65.1  D. 65.136</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.00025648 тоог 2 тэмдэгтээр тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 0.00025  B. 0.00026  C. 0.0003  D. 0.000256</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Усан сангийн эзлэхүүн 236.082 м$^3$ бол 5 тэмдэгтээр тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 236.08  B. 236.1  C. 236.09  D. 236.00</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Гурвалжны талууд 9, 12, 15 бол түүний талбайг ол.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 54  B. 90  C. 108  D. 45</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Тэгш өнцөгтийн талууд 5 см ба 12 см бол диагоналийн уртыг ол.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 66A. 13 см  B. 15 см  C. 17 см  D. 14 см</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Кубийн ирмэг 4 см бол түүний диагональ огтлолын талбай?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $16\sqrt{2}$ см$^2$  B. 16 см$^2$  C. $16\sqrt{3}$ см$^2$  D. 32 см$^2$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>10%-ийн 150 г уусмал дээр 5%-ийн 60 г уусмал нэмэхэд концентраци хэд болох вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 8.57%  B. 9%  C. 7.5%  D. 8%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Буудлагын тамирчин байг онох магадлал 0.6 ба 0.7 бол хоёулаа онохгүй байх магадлал?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 0.12  B. 0.42  C. 0.13  D. 0.18</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Гэрлийн хурд $3 \times 10^8$ м/с-ийг км/с нэгжид шилжүүл.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 300,000 км/с  B. 3,000,000 км/с  C. 30,000 км/с  D. 3,000 км/с</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$0.019 \times 10^{-8}$ тоог стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $1.9 \times 10^{-10}$  B. $1.9 \times 10^{-9}$  C. $19 \times 10^{-10}$  D. $1.9 \times 10^{-7}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Дэлхийн экваторын радиус 6378.1 км бол үүнийг стандарт дүрсээр метрээр илэрхийл.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $6.3781 \times 10^6$ м  B. $63.781 \times 10^5$ м  C. $6.3 \times 10^6$ м  D. $6.3781 \times 10^3$ м</t>
     </r>
   </si>
 </sst>
@@ -2328,7 +2328,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>6</v>
@@ -2342,7 +2342,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>6</v>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>7</v>
@@ -2370,7 +2370,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>7</v>
@@ -2384,7 +2384,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>8</v>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>7</v>
@@ -2412,7 +2412,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>6</v>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>7</v>
@@ -2440,7 +2440,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>6</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>6</v>
@@ -2468,7 +2468,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>7</v>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>7</v>
@@ -2496,7 +2496,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>7</v>
@@ -2510,7 +2510,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>7</v>
@@ -2524,7 +2524,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>6</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>7</v>
@@ -2552,7 +2552,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>4</v>
@@ -2566,7 +2566,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>7</v>
@@ -2580,7 +2580,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>8</v>
@@ -2594,7 +2594,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>7</v>
@@ -2608,7 +2608,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>6</v>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>7</v>
@@ -2636,7 +2636,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>6</v>
@@ -2650,7 +2650,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>6</v>
@@ -2664,7 +2664,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>6</v>
@@ -2678,7 +2678,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>6</v>
@@ -2692,7 +2692,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>6</v>
@@ -2706,7 +2706,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>7</v>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>6</v>
@@ -2734,7 +2734,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>7</v>
@@ -2748,7 +2748,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>6</v>
@@ -2762,7 +2762,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>6</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>6</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>7</v>
@@ -2804,7 +2804,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>6</v>
@@ -2818,7 +2818,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>7</v>
@@ -2832,7 +2832,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>7</v>
@@ -2846,7 +2846,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>7</v>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>8</v>
@@ -2874,7 +2874,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>7</v>
@@ -2888,7 +2888,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>6</v>
@@ -2902,7 +2902,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>6</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>6</v>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>7</v>
@@ -2944,7 +2944,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>7</v>
@@ -2958,7 +2958,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>6</v>
@@ -2972,7 +2972,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>6</v>
@@ -2986,7 +2986,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>6</v>
@@ -3000,7 +3000,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>7</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>6</v>
@@ -3028,7 +3028,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B64" s="8" t="s">
         <v>8</v>
@@ -3042,7 +3042,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>6</v>
@@ -3056,7 +3056,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>6</v>
@@ -3070,7 +3070,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>6</v>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B68" s="8" t="s">
         <v>6</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B69" s="8" t="s">
         <v>7</v>
@@ -3112,7 +3112,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B70" s="8" t="s">
         <v>7</v>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>6</v>
@@ -3140,7 +3140,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>8</v>
@@ -3154,7 +3154,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>6</v>
@@ -3168,7 +3168,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>6</v>
@@ -3182,7 +3182,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B75" s="8" t="s">
         <v>7</v>
@@ -3196,7 +3196,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>7</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>7</v>
@@ -3224,7 +3224,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B78" s="8" t="s">
         <v>7</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>6</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>6</v>
@@ -3266,7 +3266,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>7</v>
@@ -3280,7 +3280,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>7</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>7</v>
@@ -3308,7 +3308,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>6</v>
@@ -3322,7 +3322,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>6</v>
@@ -3336,7 +3336,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>6</v>
@@ -3350,7 +3350,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>7</v>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>6</v>
@@ -3378,7 +3378,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>6</v>
@@ -3392,7 +3392,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>7</v>
@@ -3406,7 +3406,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>6</v>
@@ -3420,7 +3420,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B92" s="8" t="s">
         <v>6</v>
@@ -3434,7 +3434,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B93" s="8" t="s">
         <v>7</v>
@@ -3448,7 +3448,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>7</v>
@@ -3462,7 +3462,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B95" s="8" t="s">
         <v>7</v>
@@ -3476,7 +3476,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B96" s="8" t="s">
         <v>7</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B97" s="8" t="s">
         <v>7</v>
@@ -3504,7 +3504,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B98" s="8" t="s">
         <v>7</v>
@@ -3518,7 +3518,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B99" s="8" t="s">
         <v>7</v>
@@ -3532,7 +3532,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B100" s="8" t="s">
         <v>7</v>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>7</v>

--- a/task_1_3.xlsx
+++ b/task_1_3.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\math_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6EC3BA-4B6A-49FE-A0FE-99579AEA80D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07FE7F8-C4BA-4164-A5E3-278B4589853B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3D11977B-6E7B-425F-AD88-162E10A9900B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_rb1o49cm72wg" localSheetId="0">Sheet1!$A$102</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -68,1411 +71,311 @@
     <t>Хэрэглээ</t>
   </si>
   <si>
-    <r>
-      <t>Инженерүүд түлш хэмнэхээр хөлөг онгоцыг 150 м өндөрт хөөрөх дарвуулаар тоногложээ. Дарвуул онгоцыг 45° өнцгөөр татаж байвал олсны урт ойролцоогоор хэд байх вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 150 м  B. 212 м  C. 300 м  D. 106 м</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Дарвуулт хөлгийн олсны урт 212 м бол хөлөг онгоцны тавцангаас дарвуулын суурь хүртэлх хэвтээ зайг Пифагорын теорем ашиглан ол.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 150 м  B. 173 м  C. 212 м  D. 200 м</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Салхин сэнсний нэг далавчны урт 40 м. Хоёр цамхаг хоорондын аюулгүй зай нь далавчны уртаас 5 дахин их байх ёстой бол энэ зай хэд вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 80 м  B. 160 м  C. 200 м  D. 400 м</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хоёр цамхгийн хоорондох зайг 177 м гэж тооцоолсон бол энэ нь аюулгүй байдлын дүрмийг (хамгийн багадаа 200 м байх) хангасан уу?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. Хангасан  B. Хангаагүй  C. Тэнцүү  D. Тодорхойгүй</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Гэрлийн хурд $3 \times 10^8$ м/с. Бархасбадь гараг нарнаас 778 сая км-ийн зайд оршдог бол гэрэл очиход хэдэн минут зарцуулах вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 40 мин  B. 43 мин  C. 50 мин  D. 53 мин</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Тэгш өнцөгтийн урт 12 см, өргөн 7 см (см-ээр тоймлосон утга). Уртын авч болох хамгийн их утга хэд вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 12.4 см  B. 12.5 см  C. 12.49 см  D. 13 см</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Тэгш өнцөгтийн өргөнийг см-ээр тоймлоход 7 см болсон бол түүний авч болох хамгийн бага утгыг ол.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 6.4 см  B. 6.5 см  C. 6.6 см  D. 7.0 см</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Урт нь 12 см, өргөн нь 7 см (тоймлосон утга) тэгш өнцөгтийн талбайн авч болох хамгийн их утгыг ол.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 84 см$^2$  B. 93.75 см$^2$  C. 90.25 см$^2$  D. 83.25 см$^2$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Гэрийн шалны радиусыг метрээр тоймлоход 3 м болжээ. Гэрийн шалны диаметр хамгийн ихдээ хэд байх вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 6 м  B. 6.5 м  C. 7 м  D. 5.5 м</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Радиус нь 3 м (тоймлосон) гэрийн шалны талбайн авч болох хамгийн бага утгыг ол ($\pi = 3.14$).</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 28.26 м$^2$  B. 19.625 м$^2$  C. 25.0 м$^2$  D. 38.465 м$^2$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хөндий блокийн массыг 0.01 нарийвчлалтай тоймлоход 0.20 кг болжээ. Массын авч болох хамгийн бага утга?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 0.19 кг  B. 0.195 кг  C. 0.199 кг  D. 0.20 кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Эзлэхүүнийг 0.01 нарийвчлалтай тоймлоход 0.04 м$^3$ болсон бол эзлэхүүний хамгийн их утга хэд вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 0.044 м$^3$  B. 0.045 м$^3$  C. 0.035 м$^3$  D. 0.05 м$^3$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Дугтуйны уртыг см-ээр тоймлоход 21 см байв. Дугтуйны урт хамгийн багадаа ямар байх вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 20 см  B. 20.5 см  C. 20.4 см  D. 21.0 см</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Ил захидлын уртыг 0.1 нарийвчлалтай тоймлоход 20.5 см болжээ. Ил захидлын уртын хамгийн их утга?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 20.55 см  B. 20.54 см  C. 20.6 см  D. 21.0 см</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>20.5 см-ийн (0.1 нарийвчлалтай тоймлосон) ил захидал 21 см-ийн (см-ээр тоймлосон) дугтуйд багтах уу?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. Багтана  B. Багтахгүй  C. Заримдаа  D. Тодорхойгүй</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хүний бие дунджаар $10^{14}$ ширхэг эсээс тогтдог. Нэг эс 1 нг жинтэй бол биеийн нийт эсийн массыг кг-аар илэрхийл.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 0.1 кг  B. 10 кг  C. 100 кг  D. 1 кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Дэлхийн масс ойролцоогоор $5.97 \times 10^{24}$ кг бол үүнийг тонн нэгжээр стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $5.97 \times 10^{21}$ т  B. $5.97 \times 10^{27}$ т  C. $5.97 \times 10^{18}$ т  D. $5.97 \times 10^{24}$ т</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Савангийн хөөсний зузаан $0.0000001$ м бол үүнийг 10-ын зэрэг оролцсон стандарт хэлбэрт бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $10^{-6}$ м  B. $10^{-7}$ м  C. $10^{-8}$ м  D. $1 \times 10^7$ м</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Нарны гэрэл дэлхий рүү 8 минутад ирдэг. Гэрлийн хурд $3 \times 10^8$ м/с бол нарнаас дэлхий хүртэлх зайг км-ээр илэрхийл.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 144 сая км  B. 150 сая км  C. 1.44 сая км  D. 15 сая км</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Австралийн газар нутаг 7,692,024 км$^2$, Коста-Рика 51,100 км$^2$. Австрали Коста-Рикагаас ойролцоогоор хэд дахин их вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 100 дахин  B. 154 дахин  C. 21 дахин  D. 150 дахин</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$1.5$ см ирмэгтэй жижиг куб ба 5 см ирмэгтэй том кубийн эзлэхүүнүүдийн харьцааг бүхлээр тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 3 дахин  B. 37 дахин  C. 10 дахин  D. 25 дахин</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Од эрхэс дэлхийгээс 500 гэрлийн жилийн зайд оршдог. Энэ зайг км-ээр илэрхийлж стандарт дүрсэд бич ($1$ г.ж $\approx 9.46 \times 10^{12}$ км).</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $4.73 \times 10^{15}$ км  B. $47.3 \times 10^{14}$ км  C. $4.73 \times 10^{12}$ км  D. $9.46 \times 10^{14}$ км</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Бичгийн цаасны зузаан $0.0000213$ м бол үүнийг мм нэгжээр стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $2.13 \times 10^{-2}$ мм  B. $21.3 \times 10^{-3}$ мм  C. $0.213$ мм  D. $2.13 \times 10^{-5}$ мм</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Билгүүн нэг тоог 2.6 гэж (0.1 нарийвчлалтай), Марал 2.639 гэж тоймложээ. Уг тоо 2.6387 байх боломжтой юу?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. Боломжтой  B. Боломжгүй  C. Маралынх буруу  D. Билгүүнийх буруу</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Кубийн эзлэхүүнийг Билгүүн 3.7, Марал 3.75 гэж тоймлосон нь хоёул зөв бол эзлэхүүний авч болох хамгийн бага утга?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 3.745  B. 3.70  C. 3.65  D. 3.74</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Цаасны массыг 1 мг-аар илэрхийлэхдээ 10-ын зэрэг ашиглавал хэдэн кг болох вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $10^{-3}$ кг  B. $10^{-6}$ кг  C. $10^6$ кг  D. $10^{-9}$ кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Дэлхийн экваторын радиус 6378.1 км бол үүнийг метрээр илэрхийлж стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $6.3781 \times 10^6$ м  B. $6.3781 \times 10^3$ м  C. $63.781 \times 10^5$ м  D. $6.3781 \times 10^7$ м</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Нэхмэлчид хивс нэхэхдээ урт нь 36 см, өргөн нь 28 см байх хээ үүсгэв. Тэгш хэмтэй хээний хамгийн бага хэмжээ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 120 см  B. 4 см  C. 92.2 см  D. 252 см</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Усан сангийн урт 10.3 м, өргөн 6.2 м, өндөр 3.7 м бол эзлэхүүнийг 0.1 нарийвчлалтай тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 236.3 м$^3$  B. 236.1 м$^3$  C. 236.0 м$^3$  D. 236.08 м$^3$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Гэрлийн жил нь $946,100,000,000,000,000$ м бол үүнийг стандарт дүрсээр бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $9.461 \times 10^{17}$ м  B. $9.461 \times 10^{12}$ м  C. $9.461 \times 10^{15}$ м  D. $0.946 \times 10^{18}$ м</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хөлийн хумс цагт $0.000,000,000,007,323$ м ургадаг бол мм-ээр стандарт дүрсээр бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $7.323 \times 10^{-9}$ мм  B. $7.323 \times 10^{-12}$ мм  C. $7.323 \times 10^{-8}$ мм  D. $0.732 \times 10^{-9}$ мм</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Бумба хэлбэртэй савны радиусыг дециметрээр тоймлоход 16 дм болжээ. Эзлэхүүний авч болох хамгийн их утга?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 17157 дм$^3$  B. 22438 дм$^3$  C. 18807 дм$^3$  D. 20000 дм$^3$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Радиус нь 16 дм (тоймлосон) бумбын эзлэхүүний хамгийн бага утга?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 15591 дм$^3$  B. 16000 дм$^3$  C. 14000 дм$^3$  D. 18807 дм$^3$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Тэгш өнцөгт параллелепипедийн талууд 1, $\sqrt{3}, \sqrt{5}$ бол эзлэхүүнийг 0.1-ээр тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 3.8  B. 3.9  C. 4.0  D. 3.3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Эверестийн оргил 29029 тохой бол $x \times 10^y$ хэлбэрт (x, y - нэг оронтой) бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $2.9 \times 10^4$  B. $3 \times 10^4$  C. $29 \times 10^3$  D. $0.3 \times 10^5$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Машины дугуй 0.6 м диаметртэй. 1 км явахад дугуй хэдэн удаа эргэх вэ? (Бүхлээр тоймло)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 530  B. 531  C. 500  D. 600</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">650 мл-ийн 15% хэдэн мл болох вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 9.75 мл  B. 97.5 мл  C. 975 мл  D. 0.975 мл</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Цилиндр савны өндөр 65 см, диаметр 40 см. 1 литр элс 2 кг жинтэй бол саванд хэдэн кг элс орох вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 150 кг  B. 163.28 кг  C. 160 кг  D. 170 кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Төсөөтэй хоёр биетийн талбайн харьцаа $k^2=4$ бол ирмэгийн харьцаа хэд вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 2  B. 4  C. 8  D. 16</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Төсөөтэй биетийн эзлэхүүний харьцаа $k^3=27$ бол гадаргуугийн талбайн харьцаа?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 3  B. 9  C. 27  D. 81</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Төсөөтэй биетийн эзлэхүүний харьцаа $k^3=125$ бол ирмэгийн харьцаа?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 5  B. 25  C. 10  D. 50</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Угаалгын шингэн 650 мл ба 25% нэмэгдэлтэй бол ердийн савны хэмжээ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 500 мл  B. 520 мл  C. 480 мл  D. 600 мл</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Гар чийдэнгийн зай 12 цаг ажилладаг ба 30 мин нэмэгдсэн бол хэдэн хувиар өссөн бэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 4%  B. 4.17%  C. 5%  D. 10%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хуурай мөөгөнд 12% ус, шинэ мөөгөнд 90% ус байдаг. 22 кг шинэ мөөгнөөс хэдэн кг хуурай мөөг авах вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 2.2 кг  B. 2.5 кг  C. 3 кг  D. 1.8 кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1 литр 6%-ийн спиртээс 5% болгоход хэдэн литр 3%-ийн спирт нэмэх вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 0.5 л  B. 1 л  C. 0.2 л  D. 0.8 л</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$2^{3x} = 64$ бол $x$-ийг ол.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 40A. 1  B. 2  C. 3  D. 4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$8^{x+1} = 4$ хялбар илтгэгч тэгшитгэлийг бод.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. -1/3  B. 1/3  C. 3  D. 5/3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$27^x = 9$ илтгэгч тэгшитгэлийн шийд?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 2/3  B. 3/2  C. 1/2  D. 1/3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$100 \div 10^{-3}$ үйлдлийн хариуг 10-ын зэргээр илэрхийл.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $10^5$  B. $10^2$  C. $10^{-1}$  D. $10^1$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Нарны масс ойролцоогоор $1.98 \times 10^{30}$ кг байдаг. Үүнийг аравтын бутархайгаар бичвэл 8-ын цифрийн ард хэдэн тэг бичигдэх вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 30  B. 29  C. 28  D. 31</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Андромед галактик хүртэлх зай ойролцоогоор $2 \times 10^{19}$ км. Үүнийг гэрлийн жилээр илэрхийл ($1$ г.ж $\approx 9.46 \times 10^{12}$ км).</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 2.1 сая г.ж  B. 1.5 сая г.ж  C. 3 сая г.ж  D. 0.5 сая г.ж</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Монгол улсын газар нутаг 1,564,116 км$^2$ бол үүнийг стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $1.564116 \times 10^6$  B. $15.6 \times 10^5$  C. $1.5 \times 10^6$  D. $156.4 \times 10^4$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хүний өндөгөн эс ойролцоогоор 1 нг (нанограмм) жинтэй. Үүнийг кг нэгжээр стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $10^{-9}$ кг  B. $10^{-12}$ кг  C. $10^{-6}$ кг  D. $10^{-15}$ кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Бичил биетний урт 3.6 $\mu$г (микрограмм). Үүнийг кг нэгжээр стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $3.6 \times 10^{-6}$ кг  B. $3.6 \times 10^{-9}$ кг  C. $3.6 \times 10^{-12}$ кг  D. $3.6 \times 10^9$ кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Дэлхийн экваторын бүс 40075.012 км бол үүнийг 0.1 нарийвчлалтай тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 40075.0  B. 40075.1  C. 40075  D. 40080</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$16 \times 10^7$ тоо нь $4 \times 10^3$ тооноос хэд дахин их вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $4 \times 10^4$  B. $4 \times 10^{10}$  C. 4000  D. 400</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Инженерүүд салхин сэнсний цамхгийг барихад нэг цамхагт 3.2 сая доллар зарцуулдаг. 3 цамхаг барих зардлыг стандарт дүрсээр бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $9.6 \times 10^5$  B. $9.6 \times 10^6$  C. $0.96 \times 10^7$  D. $96 \times 10^6$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Салхин сэнсний засвар үйлчилгээний зардал жилд 400,000 доллар. Үүнийг 10-ын зэрэг ашиглан бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $4 \times 10^4$  B. $4 \times 10^5$  C. $0.4 \times 10^6$  D. $40 \times 10^4$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Тэгш өнцөгт талбайн урт 13 см, өргөн 8 см (см-ээр тоймлосон). Талбайн авч болох хамгийн их утга?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 104 см$^2$  B. 114.75 см$^2$  C. 108.25 см$^2$  D. 110 см$^2$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Бархасбадь гараг нарнаас 778 сая км зайд оршдог. Гэрэл (хурд $3 \times 10^5$ км/с) Бархасбадь хүртэл хэдэн секундэд очих вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 2593 сек  B. 2334 сек  C. 1500 сек  D. 3000 сек</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хайрцагны өндөр 4 см, гадаргуугийн талбай нь 96 см$^2$. Төсөөтэй том хайрцагны талбай 864 см$^2$ бол том хайрцагны өндөр?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 8 см  B. 12 см  C. 16 см  D. 24 см</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Жижиг хайрцагны эзлэхүүн 64 см$^3$, том хайрцагны талбайн харьцаа $k^2=9$ бол том хайрцагны эзлэхүүн?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 192 см$^3$  B. 576 см$^3$  C. 1728 см$^3$  D. 512 см$^3$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Савангийн хөөсний зузаан $0.0000001$ м бол үүнийг $1 \times 10^n$ дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $n = -6$  B. $n = -7$  C. $n = -8$  D. $n = 7$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хүний биеийн эсийн масс 100 кг ба нэг эс 1 нг бол нийт эсийн тоог стандарт дүрсээр бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $1 \times 10^{11}$  B. $1 \times 10^{14}$  C. $1 \times 10^{15}$  D. $1 \times 10^{12}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Австралийн газар нутаг ойролцоогоор 7.7 сая км$^2$, Коста Рика 51 мянган км$^2$. Австрали хэд дахин их вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 100 дахин  B. 150 дахин  C. 200 дахин  D. 50 дахин</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Квадратын тал $\sqrt{50}$ см бол түүний талыг 0.1 нарийвчлалтай тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 7.0 см  B. 7.1 см  C. 7.07 см  D. 7.2 см</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Од хүртэлх зай 500 гэрлийн жил бол км-ээр илэрхийлж 2 тэмдэгтээр тоймло ($1$ г.ж $\approx 9.5 \times 10^{12}$ км).</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $4.8 \times 10^{15}$ км  B. $4.7 \times 10^{15}$ км  C. $5.0 \times 10^{14}$ км  D. $9.5 \times 10^{14}$ км</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$325.78$ тоог 3 тэмдэгтээр тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 54, 55A. 326  B. 325  C. 330  D. 325.8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$95 \times 212$ үржвэрийг тоог тоймлох замаар багцаалж ол.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 18,000  B. 20,000  C. 21,000  D. 19,000</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$77.9 \times 22.6$ үйлдлийг тоймлож гүйцэтгэхэд гарах багцаа утга?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 1600  B. 1760  C. 1800  D. 1500</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Радиус нь 16 дм (тоймлосон) бөмбөрцгийн эзлэхүүний дээд хязгаар?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 18807 дм$^3$  B. 22438 дм$^3$  C. 20000 дм$^3$  D. 21000 дм$^3$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Гэрийн шалны радиус 3 м (тоймлосон). Талбайн авч болох дээд утга ($S=\pi r^2$)?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 28.26 м$^2$  B. 38.465 м$^2$  C. 30.0 м$^2$  D. 35.5 м$^2$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Гурилын жинг 0.5 нарийвчлалтай тоймлоход 169.5 кг болсон бол хамгийн бага жин?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 169.25 кг  B. 169.0 кг  C. 169.4 кг  D. 169.45 кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$59,588$ тоог нэг тэмдэгтээр тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 60,000  B. 50,000  C. 59,000  D. 6,000</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$3.9 \times 10^8 \times 2.6 \times 10^{-5}$ үржвэрийг стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $1.014 \times 10^4$  B. $10.14 \times 10^3$  C. $1.014 \times 10^3$  D. $1.0 \times 10^4$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$0.00000089$ тоог стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $8.9 \times 10^{-7}$  B. $8.9 \times 10^{-6}$  C. $0.89 \times 10^{-6}$  D. $8.9 \times 10^{-8}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>15 их наяд тоог стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $1.5 \times 10^{12}$  B. $1.5 \times 10^{13}$  C. $15 \times 10^{12}$  D. $1.5 \times 10^{11}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1 нг (нанограмм)-ийг кг-аар илэрхийл.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $10^{-9}$ кг  B. $10^{-12}$ кг  C. $10^{-6}$ кг  D. $10^{-10}$ кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3.6 $\mu$г (микрограмм)-ийг кг-аар илэрхийл.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $3.6 \times 10^{-9}$ кг  B. $3.6 \times 10^{-6}$ кг  C. $3.6 \times 10^{-12}$ кг  D. $3.6 \times 10^{-10}$ кг</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хөлөг онгоц дарвуул ашиглан жилд 3.5 сая литр түлш хэрэглэдэг. Дарвуул 20% хэмнэдэг бол хэдэн литр түлш хэмнэх вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 7, 62A. 700,000 л  B. 500,000 л  C. 800,000 л  D. 1,000,000 л</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Түлшний үнэ 0.42 Z/литр бол жилд хэмнэх 700,000 литр түлшний үнийг ол.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 294,000 Z  B. 300,000 Z  C. 250,000 Z  D. 350,000 Z</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Салхин сэнсний далавчны урт 40 м. Аюулгүй зай нь далавчны уртаас 5 дахин их бол энэ зай хэд вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 160 м  B. 200 м  C. 250 м  D. 300 м</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хоёр цамхгийн хоорондох зай 177 м бол аюулгүй байдлын 200 м-ийн дүрмийг хангасан уу?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. Хангасан  B. Хангаагүй  C. Тэнцүү  D. Мэдэх боломжгүй</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Салхин сэнс барихад 2.5 сая доллар зарцуулсан. Жилд 294,000 доллар хэмнэдэг бол хэдэн жилийн дараа зардлаа нөхөх вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 5-6 жил  B. 8-9 жил  C. 10 жил  D. 12 жил</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Сэнсний дээд хурд 300 км/ц бол үүнийг м/с нэгжид шилжүүлж бүхлээр тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 8A. 83 м/с  B. 100 м/с  C. 50 м/с  D. 120 м/с</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хурдны нэгжийг шилжүүл: 150 м/с хэдэн км/ц болох вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 450 км/ц  B. 540 км/ц  C. 300 км/ц  D. 600 км/ц</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Хурдны нэгжийг шилжүүл: 300 м/с хэдэн км/ц болох вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 1000 км/ц  B. 1080 км/ц  C. 900 км/ц  D. 1200 км/ц</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Төсөөтэй хоёр дүрсийн талбайн харьцаа $k^2 = 4/121$ бол ирмэгийн харьцаа?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 2/11  B. 4/11  C. 2/121  D. 16/121</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>65.1359 тоог 0.01 нарийвчлалтай тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 65.13  B. 65.14  C. 65.1  D. 65.136</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.00025648 тоог 2 тэмдэгтээр тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 0.00025  B. 0.00026  C. 0.0003  D. 0.000256</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Усан сангийн эзлэхүүн 236.082 м$^3$ бол 5 тэмдэгтээр тоймло.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 236.08  B. 236.1  C. 236.09  D. 236.00</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Гурвалжны талууд 9, 12, 15 бол түүний талбайг ол.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 54  B. 90  C. 108  D. 45</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Тэгш өнцөгтийн талууд 5 см ба 12 см бол диагоналийн уртыг ол.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 66A. 13 см  B. 15 см  C. 17 см  D. 14 см</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Кубийн ирмэг 4 см бол түүний диагональ огтлолын талбай?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $16\sqrt{2}$ см$^2$  B. 16 см$^2$  C. $16\sqrt{3}$ см$^2$  D. 32 см$^2$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>10%-ийн 150 г уусмал дээр 5%-ийн 60 г уусмал нэмэхэд концентраци хэд болох вэ?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 8.57%  B. 9%  C. 7.5%  D. 8%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Буудлагын тамирчин байг онох магадлал 0.6 ба 0.7 бол хоёулаа онохгүй байх магадлал?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 0.12  B. 0.42  C. 0.13  D. 0.18</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Гэрлийн хурд $3 \times 10^8$ м/с-ийг км/с нэгжид шилжүүл.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 300,000 км/с  B. 3,000,000 км/с  C. 30,000 км/с  D. 3,000 км/с</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$0.019 \times 10^{-8}$ тоог стандарт дүрсэд бич.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $1.9 \times 10^{-10}$  B. $1.9 \times 10^{-9}$  C. $19 \times 10^{-10}$  D. $1.9 \times 10^{-7}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Дэлхийн экваторын радиус 6378.1 км бол үүнийг стандарт дүрсээр метрээр илэрхийл.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. $6.3781 \times 10^6$ м  B. $63.781 \times 10^5$ м  C. $6.3 \times 10^6$ м  D. $6.3781 \times 10^3$ м</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$Нягт = масс / эзлэхүүн$ бол дээрх блокийн нягтын авч болох хамгийн бага утгыг ол.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A. 4.3  B. 4.6  C. 5.0  D. 5.7</t>
-    </r>
+    <t>Инженерүүд түлш хэмнэхээр хөлөг онгоцыг 150 м өндөрт хөөрөх дарвуулаар тоногложээ. Дарвуул онгоцыг $45^\circ$ өнцгөөр татаж байвал олсны урт ойролцоогоор хэдэн метр байх вэ? ($\sin 45^\circ \approx 0.707$)A. 150 м  B. 212 м  C. 300 м  D. 106 м</t>
+  </si>
+  <si>
+    <t>Дарвуулт хөлгийн олсны урт 212 м бол хөлөг онгоцны тавцангаас дарвуулын суурь хүртэлх хэвтээ зайг Пифагорын теорем ашиглан ол.A. 150 м  B. 173 м  C. 212 м  D. 200 м</t>
+  </si>
+  <si>
+    <t>Салхин сэнсний нэг далавчны урт 40 м. Хоёр цамхаг хоорондын хамгийн бага зай нь далавчны уртаас 5 дахин их байх ёстой бол энэ зай хэд вэ?A. 80 м  B. 160 м  C. 200 м  D. 400 м</t>
+  </si>
+  <si>
+    <t>Хоёр цамхгийн хоорондох зайг 177 м гэж тооцоолсон бол энэ нь аюулгүй байдлын дүрмийг (хамгийн багадаа 200 м байх) хангасан уу?A. Хангасан  B. Хангаагүй  C. Тэнцүү  D. Тодорхойгүй</t>
+  </si>
+  <si>
+    <t>Гэрлийн хурд $3 \times 10^8$ м/с. Бархасбадь гараг нарнаас 778 сая км-ийн зайд оршдог бол гэрэл очиход хэдэн минут зарцуулах вэ?A. 40 мин  B. 43 мин  C. 50 мин  D. 53 мин</t>
+  </si>
+  <si>
+    <t>Тэгш өнцөгтийн урт 12 см, өргөн 7 см (см-ээр тоймлосон утга). Уртын авч болох хамгийн их утга хэд вэ?A. 12.4 см  B. 12.5 см  C. 12.49 см  D. 13 см</t>
+  </si>
+  <si>
+    <t>Тэгш өнцөгтийн өргөнийг см-ээр тоймлоход 7 см болсон бол түүний авч болох хамгийн бага утгыг ол.A. 6.4 см  B. 6.5 см  C. 6.6 см  D. 7.0 см</t>
+  </si>
+  <si>
+    <t>Урт нь 12 см, өргөн нь 7 см (тоймлосон утга) тэгш өнцөгтийн талбайн авч болох хамгийн их утгыг ол.A. 84 см$^2$  B. 93.75 см$^2$  C. 90.25 см$^2$  D. 83.25 см$^2$</t>
+  </si>
+  <si>
+    <t>Таван ханатай гэрийн шалны радиусыг метрээр тоймлоход 3 м болжээ. Гэрийн шалны диаметр хамгийн ихдээ хэд байх вэ?A. 6 м  B. 6.5 м  C. 7 м  D. 5.5 м</t>
+  </si>
+  <si>
+    <t>Радиус нь 3 м (тоймлосон) гэрийн шалны талбайн авч болох хамгийн бага утгыг ол. ($\pi \approx 3.14$)A. 28.26 м$^2$  B. 19.625 м$^2$  C. 25 м$^2$  D. 38.465 м$^2$</t>
+  </si>
+  <si>
+    <t>Хөндий блокийн массыг 0.01 нарийвчлалтай тоймлоход 0.20 кг болжээ. Массын авч болох хамгийн бага утга?A. 0.19 кг  B. 0.195 кг  C. 0.199 кг  D. 0.20 кг</t>
+  </si>
+  <si>
+    <t>Эзлэхүүнийг 0.01 нарийвчлалтай тоймлоход 0.04 м$^3$ болсон бол эзлэхүүний хамгийн их утга хэд вэ?A. 0.044 м$^3$  B. 0.045 м$^3$  C. 0.035 м$^3$  D. 0.05 м$^3$</t>
+  </si>
+  <si>
+    <t>Нягт = масс / эзлэхүүн бол дээрх блокийн нягтын авч болох хамгийн бага утгыг ол.A. 4.3  B. 4.6  C. 5.0  D. 5.7</t>
+  </si>
+  <si>
+    <t>Дугтуйны уртыг см-ээр тоймлоход 21 см байв. Дугтуйны урт хамгийн багадаа ямар байх вэ?A. 20 см  B. 20.5 см  C. 20.4 см  D. 21.0 см</t>
+  </si>
+  <si>
+    <t>Ил захидлын уртыг 0.1 нарийвчлалтай тоймлоход 20.5 см болжээ. Ил захидлын уртын хамгийн их утга?A. 20.55 см  B. 20.54 см  C. 20.6 см  D. 21.0 см</t>
+  </si>
+  <si>
+    <t>20.5 см-ийн (0.1 нарийвчлалтай тоймлосон) ил захидал 21 см-ийн (см-ээр тоймлосон) дугтуйд багтах уу?A. Багтана  B. Багтахгүй  C. Заримдаа  D. Тодорхойгүй</t>
+  </si>
+  <si>
+    <t>Хүний бие дунджаар $10^{14}$ ширхэг эсээс тогтдог. Нэг эс 1 нг (нанограмм) жинтэй бол биеийн нийт эсийн массыг кг-аар илэрхийл.A. 0.1 кг  B. 10 кг  C. 100 кг  D. 1 кг</t>
+  </si>
+  <si>
+    <t>Дэлхийн масс ойролцоогоор $5.97 \times 10^{24}$ кг бол үүнийг тонн нэгжээр стандарт дүрсэд бич.A. $5.97 \times 10^{21}$ т  B. $5.97 \times 10^{27}$ т  C. $5.97 \times 10^{18}$ т  D. $5.97 \times 10^{24}$ т</t>
+  </si>
+  <si>
+    <t>Савангийн хөөсний зузаан $0.0000001$ м бол үүнийг $10$-ын зэрэг оролцсон стандарт хэлбэрт бич.A. $10^{-6}$ м  B. $10^{-7}$ м  C. $10^{-8}$ м  D. $1 \times 10^7$ м</t>
+  </si>
+  <si>
+    <t>Нарны гэрэл дэлхий рүү 8 минутад ирдэг. Гэрлийн хурд $3 \times 10^8$ м/с бол нарнаас дэлхий хүртэлх зайг км-ээр илэрхийл.A. 144 сая км  B. 150 сая км  C. 1.44 сая км  D. 15 сая км</t>
+  </si>
+  <si>
+    <t>Австралийн газар нутаг 7,692,024 км$^2$, Коста-Рика 51,100 км$^2$. Австрали Коста-Рикагаас ойролцоогоор хэд дахин их вэ?A. 100 дахин  B. 154 дахин  C. 21 дахин  D. 150 дахин</t>
+  </si>
+  <si>
+    <t>$1.5$ см ирмэгтэй жижиг куб ба 5 см ирмэгтэй том кубийн эзлэхүүнүүдийн харьцааг бүхлээр тоймло.A. 3 дахин  B. 37 дахин  C. 10 дахин  D. 25 дахин</t>
+  </si>
+  <si>
+    <t>Од эрхэс дэлхийгээс 500 гэрлийн жилийн зайд оршдог. Энэ зайг км-ээр илэрхийлж стандарт дүрсэд бич. (1 г.ж $\approx 9.46 \times 10^{12}$ км)A. $4.73 \times 10^{15}$ км  B. $4.73 \times 10^{14}$ км  C. $4.73 \times 10^{12}$ км  D. $9.46 \times 10^{14}$ км</t>
+  </si>
+  <si>
+    <t>Бичгийн цаасны зузаан $0.0000213$ м бол үүнийг мм нэгжээр стандарт дүрсэд бич.A. $2.13 \times 10^{-2}$ мм  B. $21.3 \times 10^{-3}$ мм  C. $0.213$ мм  D. $2.13 \times 10^{-5}$ мм</t>
+  </si>
+  <si>
+    <t>Билгүүн нэг тоог 2.6 гэж (0.1 нарийвчлалтай), Марал 2.639 гэж тоймложжээ. Уг тоо $2.6387$ байх боломжтой юу?A. Боломжтой  B. Боломжгүй  C. Маралынх буруу  D. Билгүүнийх буруу</t>
+  </si>
+  <si>
+    <t>Кубийн эзлэхүүнийг Билгүүн 3.7, Марал 3.75 гэж тоймлосон нь хоёул зөв бол эзлэхүүний авч болох хамгийн бага утга?A. 3.745  B. 3.70  C. 3.65  D. 3.74</t>
+  </si>
+  <si>
+    <t>Цаасны массыг 1 мг-аар илэрхийлэхдээ 10-ын зэрэг ашиглавал хэдэн кг болох вэ?A. $10^{-3}$ кг  B. $10^{-6}$ кг  C. $10^6$ кг  D. $10^{-9}$ кг</t>
+  </si>
+  <si>
+    <t>Дэлхийн экваторын радиус 6378.1 км бол үүнийг метрээр илэрхийлж стандарт дүрсэд бич.A. $6.3781 \times 10^6$ м  B. $6.3781 \times 10^3$ м  C. $63.781 \times 10^5$ м  D. $6.3781 \times 10^7$ м</t>
+  </si>
+  <si>
+    <t>Нэхмэлчид хивс нэхэхдээ урт нь 36 см, өргөн нь 28 см байх хээ үүсгэв. Тэгш хэмтэй хээний хамгийн бага хэмжээ? (ХБЕХ ашиглана)A. 120 см  B. 4 см  C. 92.2 см  D. 252 см</t>
+  </si>
+  <si>
+    <t>Усан сангийн урт 10.3 м, өргөн 6.2 м, өндөр 3.7 м бол эзлэхүүнийг 0.1 нарийвчлалтай тоймло.A. 236.3 м$^3$  B. 236.1 м$^3$  C. 236.0 м$^3$  D. 236.08 м$^3$</t>
+  </si>
+  <si>
+    <t>Гэрлийн жил нь $9461000000000000$ м бол үүнийг стандарт дүрсээр бич.A. $9.461 \times 10^{15}$ м  B. $9.461 \times 10^{12}$ м  C. $9.461 \times 10^{14}$ м  D. $0.946 \times 10^{16}$ м</t>
+  </si>
+  <si>
+    <t>Хөлийн хумс цагт $0.000000000007323$ м ургадаг бол мм-ээр стандарт дүрсээр бич.A. $7.323 \times 10^{-9}$ мм  B. $7.323 \times 10^{-12}$ мм  C. $73.23 \times 10^{-10}$ мм  D. $0.732 \times 10^{-8}$ мм</t>
+  </si>
+  <si>
+    <t>Бумба хэлбэртэй савны радиусыг дециметрээр тоймлоход 16 дм болжээ. Эзлэхүүний авч болох хамгийн их утга? ($V = \frac{4}{3}\pi r^3$)A. 17157 дм$^3$  B. 18807 дм$^3$  C. 15000 дм$^3$  D. 20000 дм$^3$</t>
+  </si>
+  <si>
+    <t>Радиус нь 16 дм (тоймлосон) бумбын эзлэхүүний хамгийн бага утга?A. 15591 дм$^3$  B. 16000 дм$^3$  C. 14000 дм$^3$  D. 18000 дм$^3$</t>
+  </si>
+  <si>
+    <t>Тэгш өнцөгт параллелепипедийн талууд $1, \sqrt{3}, \sqrt{5}$ бол эзлэхүүнийг 0.1-ээр тоймло.A. 3.8  B. 3.9  C. 4.0  D. 3.7</t>
+  </si>
+  <si>
+    <t>Эверестийн оргил 29029 тохой бол $x \times 10^y$ хэлбэрт ($x, y$ - нэг оронтой) бич.A. $2.9 \times 10^4$  B. $3 \times 10^4$  C. $29 \times 10^3$  D. $0.3 \times 10^5$</t>
+  </si>
+  <si>
+    <t>Машины дугуй 0.6 м диаметртэй. 1 км явахад дугуй хэдэн удаа эргэх вэ? (Бүхлээр тоймло)A. 530  B. 531  C. 500  D. 600</t>
+  </si>
+  <si>
+    <t>Угаалгын шингэн 650 мл ба 25% нэмэгдэлтэй бол ердийн савны хэмжээ?A. 500 мл  B. 520 мл  C. 480 мл  D. 600 мл</t>
+  </si>
+  <si>
+    <t>Сав хийхэд 1 литр элс 2 кг жинтэй бол 65 см өндөр, 40 см диаметртэй цилиндр саванд хэдэн кг элс орох вэ?A. 150 кг  B. 163.28 кг  C. 160 кг  D. 170 кг</t>
+  </si>
+  <si>
+    <t>Төсөөтэй хоёр биетийн талбайн харьцаа $k^2=4$ бол ирмэгийн харьцаа хэд вэ?A. 2  B. 4  C. 8  D. 16</t>
+  </si>
+  <si>
+    <t>Төсөөтэй биетийн эзлэхүүний харьцаа $k^3=27$ бол гадаргуугийн талбайн харьцаа?A. 3  B. 9  C. 27  D. 81</t>
+  </si>
+  <si>
+    <t>Төсөөтэй биетийн эзлэхүүний харьцаа $k^3=125$ бол ирмэгийн харьцаа?A. 5  B. 25  C. 10  D. 50</t>
+  </si>
+  <si>
+    <t>Гар чийдэнгийн зай 12 цаг ажилладаг ба 30 мин нэмэгдсэн бол хэдэн хувиар өссөн бэ?A. 4%  B. 4.17%  C. 5%  D. 10%</t>
+  </si>
+  <si>
+    <t>Хуурай мөөгөнд 12% ус, шинэ мөөгөнд 90% ус байдаг. 22 кг шинэ мөөгнөөс хэдэн кг хуурай мөөг авах вэ?A. 2.2 кг  B. 2.5 кг  C. 3 кг  D. 1.8 кг</t>
+  </si>
+  <si>
+    <t>1 литр 6%-ийн спиртээс 5% болгоход хэдэн литр 3%-ийн спирт нэмэх вэ?A. 0.5 л  B. 1 л  C. 0.2 л  D. 0.8 л</t>
+  </si>
+  <si>
+    <t>$2^{3x} = 64$ бол $x$-ийг ол.A. 1  B. 2  C. 3  D. 4</t>
+  </si>
+  <si>
+    <t>$8^{x+1} = 4$ хялбар илтгэгч тэгшитгэлийг бод.A. $-1/3$  B. $1/3$  C. 3  D. $5/3$</t>
+  </si>
+  <si>
+    <t>$27^x = 9$ илтгэгч тэгшитгэлийн шийд?A. $2/3$  B. $3/2$  C. $1/2$  D. $1/3$</t>
+  </si>
+  <si>
+    <t>$100 \div 10^{-3}$ үйлдлийн хариуг 10-ын зэргээр илэрхийл.A. $10^5$  B. $10^2$  C. $10^{-1}$  D. $10^1$</t>
+  </si>
+  <si>
+    <t>Нарны масс ойролцоогоор $1.98 \times 10^{30}$ кг байдаг. Үүнийг аравтын бутархайгаар бичвэл 8-ын цифрийн ард хэдэн тэг бичигдэх вэ?A. 30  B. 29  C. 28  D. 31</t>
+  </si>
+  <si>
+    <t>Андромед галактик хүртэлх зай ойролцоогоор $2 \times 10^{19}$ км. Үүнийг гэрлийн жилээр илэрхийл. (1 г.ж $\approx 9.46 \times 10^{12}$ км)A. 2.1 сая г.ж  B. 1.5 сая г.ж  C. 3 сая г.ж  D. 0.5 сая г.ж</t>
+  </si>
+  <si>
+    <t>Монгол улсын газар нутаг 1,564,116 км$^2$ бол үүнийг стандарт дүрсэд бич.A. $1.564116 \times 10^6$  B. $15.6 \times 10^5$  C. $1.5 \times 10^6$  D. $156.4 \times 10^4$</t>
+  </si>
+  <si>
+    <t>Хүний өндөгөн эс ойролцоогоор 1 нг (нанограмм) жинтэй. Үүнийг кг нэгжээр стандарт дүрсэд бич.A. $10^{-9}$ кг  B. $10^{-12}$ кг  C. $10^{-6}$ кг  D. $10^{-15}$ кг</t>
+  </si>
+  <si>
+    <t>Бичил биетний урт 3.6 $\mu$г (микрограмм). Үүнийг кг нэгжээр стандарт дүрсэд бич.A. $3.6 \times 10^{-6}$ кг  B. $3.6 \times 10^{-9}$ кг  C. $3.6 \times 10^{-12}$ кг  D. $3.6 \times 10^9$ кг</t>
+  </si>
+  <si>
+    <t>Дэлхийн экваторын бүс 40075.012 км бол үүнийг 0.1 нарийвчлалтай тоймло.A. 40075.0  B. 40075.1  C. 40075  D. 40080</t>
+  </si>
+  <si>
+    <t>$16 \times 10^7$ тоо нь $4 \times 10^3$ тооноос хэд дахин их вэ?A. $4 \times 10^4$  B. $4 \times 10^{10}$  C. 4000  D. 400</t>
+  </si>
+  <si>
+    <t>Инженерүүд салхин сэнсний цамхгийг барихад нэг цамхагт 3.2 сая доллар зарцуулдаг. 3 цамхаг барих зардлыг стандарт дүрсээр бич.A. $9.6 \times 10^5$  B. $9.6 \times 10^6$  C. $0.96 \times 10^7$  D. $96 \times 10^6$</t>
+  </si>
+  <si>
+    <t>Салхин сэнсний засвар үйлчилгээний зардал жилд 400,000 доллар. Үүнийг 10-ын зэрэг ашиглан бич.A. $4 \times 10^4$  B. $4 \times 10^5$  C. $0.4 \times 10^6$  D. $40 \times 10^4$</t>
+  </si>
+  <si>
+    <t>Тэгш өнцөгт талбайн урт 13 см, өргөн 8 см (см-ээр тоймлосон). Талбайн авч болох хамгийн их утга?A. 104 см$^2$  B. 114.75 см$^2$  C. 108.25 см$^2$  D. 110 см$^2$</t>
+  </si>
+  <si>
+    <t>Бархасбадь гараг нарнаас 778 сая км зайд оршдог. Гэрэл (хурд $3 \times 10^5$ км/с) Бархасбадь хүртэл хэдэн секундэд очих вэ?A. 2593 сек  B. 2334 сек  C. 1500 сек  D. 3000 сек</t>
+  </si>
+  <si>
+    <t>Хайрцагны өндөр 4 см, гадаргуугийн талбай нь 96 см$^2$. Төсөөтэй том хайрцагны талбай 864 см$^2$ бол том хайрцагны өндөр?A. 8 см  B. 12 см  C. 16 см  D. 24 см</t>
+  </si>
+  <si>
+    <t>Жижиг хайрцагны эзлэхүүн 64 см$^3$, том хайрцагны талбайн харьцаа $k^2=9$ бол том хайрцагны эзлэхүүн?A. 192 см$^3$  B. 576 см$^3$  C. 1728 см$^3$  D. 512 см$^3$</t>
+  </si>
+  <si>
+    <t>Савангийн хөөсний зузаан $0.0000001$ м бол үүнийг $1 \times 10^n$ дүрсэд бич.A. $n = -6$  B. $n = -7$  C. $n = -8$  D. $n = 7$</t>
+  </si>
+  <si>
+    <t>Хүний биеийн эсийн масс 100 кг ба нэг эс 1 нг бол нийт эсийн тоог стандарт дүрсээр бич.A. $1 \times 10^{11}$  B. $1 \times 10^{14}$  C. $1 \times 10^{15}$  D. $1 \times 10^{12}$</t>
+  </si>
+  <si>
+    <t>Австралийн газар нутаг ойролцоогоор 7.7 сая км$^2$, Коста Рика 51 мянган км$^2$. Австрали ойролцоогоор хэд дахин их вэ?A. 100 дахин  B. 150 дахин  C. 200 дахин  D. 50 дахин</t>
+  </si>
+  <si>
+    <t>Квадратын тал $\sqrt{50}$ см бол түүний талыг 0.1 нарийвчлалтай тоймло.A. 7.0 см  B. 7.1 см  C. 7.07 см  D. 7.2 см</t>
+  </si>
+  <si>
+    <t>Од хүртэлх зай 500 гэрлийн жил бол км-ээр илэрхийлж 2 тэмдэгтээр тоймло.A. $4.8 \times 10^{15}$ км  B. $4.7 \times 10^{15}$ км  C. $5.0 \times 10^{14}$ км  D. $9.5 \times 10^{14}$ км</t>
+  </si>
+  <si>
+    <t>$325.78$ тоог 3 тэмдэгтээр тоймло.A. 326  B. 325  C. 330  D. 325.8</t>
+  </si>
+  <si>
+    <t>$95 \times 212$ үржвэрийг тоог тоймлох замаар багцаалж ол.A. 18,000  B. 20,000  C. 21,000  D. 19,000</t>
+  </si>
+  <si>
+    <t>$77.9 \times 22.6$ үйлдлийг тоймлож гүйцэтгэхэд гарах багцаа утга?A. 1600  B. 1760  C. 1800  D. 1500</t>
+  </si>
+  <si>
+    <t>Радиус нь 16 дм (тоймлосон) бөмбөрцгийн эзлэхүүний дээд хязгаар?A. 18807 дм$^3$  B. 22438 дм$^3$  C. 20000 дм$^3$  D. 21000 дм$^3$</t>
+  </si>
+  <si>
+    <t>Гэрийн шалны радиус 3 м (тоймлосон). Талбайн авч болох дээд утга?A. 28.26 м$^2$  B. 38.465 м$^2$  C. 30.0 м$^2$  D. 35.5 м$^2$</t>
+  </si>
+  <si>
+    <t>Гурилын жинг 0.5 нарийвчлалтай тоймлоход 169.5 кг болсон бол хамгийн бага жин?A. 169.25 кг  B. 169.0 кг  C. 169.4 кг  D. 169.45 кг</t>
+  </si>
+  <si>
+    <t>$59588$ тоог нэг тэмдэгтээр тоймло.A. 60,000  B. 50,000  C. 59,000  D. 6,000</t>
+  </si>
+  <si>
+    <t>$3.9 \times 10^8 \cdot 2.6 \times 10^{-5}$ үржвэрийг стандарт дүрсэд бич.A. $1.014 \times 10^4$  B. $10.14 \times 10^3$  C. $1.014 \times 10^3$  D. $1.0 \times 10^4$</t>
+  </si>
+  <si>
+    <t>$0.00000089$ тоог стандарт дүрсэд бич.A. $8.9 \times 10^{-7}$  B. $8.9 \times 10^{-6}$  C. $0.89 \times 10^{-6}$  D. $8.9 \times 10^{-8}$</t>
+  </si>
+  <si>
+    <t>15 их наяд тоог стандарт дүрсэд бич.A. $1.5 \times 10^{12}$  B. $1.5 \times 10^{13}$  C. $15 \times 10^{12}$  D. $1.5 \times 10^{11}$</t>
+  </si>
+  <si>
+    <t>$3.6$ $\mu$г (микрограмм)-ийг кг-аар илэрхийл.A. $3.6 \times 10^{-9}$ кг  B. $3.6 \times 10^{-6}$ кг  C. $3.6 \times 10^{-12}$ кг  D. $3.6 \times 10^{-10}$ кг</t>
+  </si>
+  <si>
+    <t>Хөлөг онгоц дарвуул ашиглан жилд 3.5 сая литр түлш хэрэглэдэг. Дарвуул 20% хэмнэдэг бол хэдэн литр түлш хэмнэх вэ?A. 700,000 л  B. 500,000 л  C. 800,000 л  D. 1,000,000 л</t>
+  </si>
+  <si>
+    <t>Түлшний үнэ 0.42 доллар/литр бол жилд хэмнэх 700,000 литр түлшний үнийг ол.A. 294,000 доллар  B. 300,000 доллар  C. 250,000 доллар  D. 350,000 доллар</t>
+  </si>
+  <si>
+    <t>Салхин сэнс барихад 2.5 сая доллар зарцуулсан. Жилд 294,000 доллар хэмнэдэг бол хэдэн жилийн дараа зардлаа нөхөх вэ?A. 5-6 жил  B. 8-9 жил  C. 10 жил  D. 12 жил</t>
+  </si>
+  <si>
+    <t>Сэнсний дээд хурд 300 км/ц бол үүнийг м/с нэгжид шилжүүлж бүхлээр тоймло.A. 83 м/с  B. 100 м/с  C. 50 м/с  D. 120 м/с</t>
+  </si>
+  <si>
+    <t>Хурдны нэгжийг шилжүүл: 150 м/с хэдэн км/ц болох вэ?A. 450 км/ц  B. 540 км/ц  C. 300 км/ц  D. 600 км/ц</t>
+  </si>
+  <si>
+    <t>Хурдны нэгжийг шилжүүл: 300 м/с хэдэн км/ц болох вэ?A. 1000 км/ц  B. 1080 км/ц  C. 900 км/ц  D. 1200 км/ц</t>
+  </si>
+  <si>
+    <t>Төсөөтэй хоёр дүрсийн талбайн харьцаа $k^2 = 4/121$ бол ирмэгийн харьцаа?A. 2/11  B. 4/11  C. 2/121  D. 16/121</t>
+  </si>
+  <si>
+    <t>$65.1359$ тоог 0.01 нарийвчлалтай тоймло.A. 65.13  B. 65.14  C. 65.1  D. 65.136</t>
+  </si>
+  <si>
+    <t>$0.00025648$ тоог 2 тэмдэгтээр тоймло.A. 0.00025  B. 0.00026  C. 0.0003  D. 0.000256</t>
+  </si>
+  <si>
+    <t>Гурвалжны талууд 9, 12, 15 бол түүний талбайг ол.A. 54  B. 90  C. 108  D. 45</t>
+  </si>
+  <si>
+    <t>Тэгш өнцөгтийн талууд 5 см ба 12 см бол диагоналийн уртыг ол.A. 13 см  B. 15 см  C. 17 см  D. 14 см</t>
+  </si>
+  <si>
+    <t>Кубийн ирмэг 4 см бол түүний диагональ огтлолын талбай?A. $16\sqrt{2}$ см$^2$  B. 16 см$^2$  C. $16\sqrt{3}$ см$^2$  D. 32 см$^2$</t>
+  </si>
+  <si>
+    <t>Гэрлийн хурд $3 \times 10^8$ м/с-ийг км/с нэгжид шилжүүл.A. 300,000 км/с  B. 3,000,000 км/с  C. 30,000 км/с  D. 3,000 км/с</t>
+  </si>
+  <si>
+    <t>$0.019 \times 10^{-8}$ тоог стандарт дүрсэд бич.A. $1.9 \times 10^{-10}$  B. $1.9 \times 10^{-9}$  C. $19 \times 10^{-10}$  D. $1.9 \times 10^{-7}$</t>
+  </si>
+  <si>
+    <t>$(\sqrt{128} - \sqrt{32})^2$ утгыг ол.A. 32  B. 64  C. 16  D. 8</t>
+  </si>
+  <si>
+    <t>Хөндий блокийн эзлэхүүний дээд хязгаар 0.045 бол 3 блокийн нийт эзлэхүүний дээд хязгаар?A. 0.135  B. 0.12  C. 0.14  D. 0.15</t>
+  </si>
+  <si>
+    <t>Гэрийн шалны диаметр 7 м-ээс бага бол түүний тойргийн уртын дээд хязгаар ($\pi \approx 3.14$)?A. 21.98 м  B. 18.84 м  C. 25 м  D. 20 м</t>
+  </si>
+  <si>
+    <t>$3.7 \times 10^{11} \cdot 9.06 \times 10^{-4}$ стандарт дүрсээр бич.A. $3.3522 \times 10^8$  B. $3.35 \times 10^8$  C. $3.3 \times 10^7$  D. $3.3522 \times 10^7$</t>
+  </si>
+  <si>
+    <t>Куб ба түүнтэй ижил эзлэхүүнтэй тэгш өнцөгт параллелепипедийн талууд $2, 4, 8$ бол кубийн ирмэг?A. 4  B. 8  C. 2  D. 16</t>
+  </si>
+  <si>
+    <t>$(\sqrt{27}+1)^2$ задалж бич.A. $28+6\sqrt{3}$  B. $28+2\sqrt{27}$  C. $29+4\sqrt{7}$  D. 30</t>
+  </si>
+  <si>
+    <t>Дарааллын 1000 дахь гишүүнийг ол: $1 \times 2, 4 \times 5, 7 \times 8, ...$A. $2998 \times 2999$  B. $2995 \times 2996$  C. $3001 \times 3002$  D. $1000 \times 1001$</t>
+  </si>
+  <si>
+    <t>$f(x) = 3x - 2$ бол $f^{-1}(7)$ утгыг ол.A. 3  B. -3  C. 2/3  D. 1/19</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1506,13 +409,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1534,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1552,11 +448,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2159,10 +1058,10 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2173,10 +1072,10 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -2187,10 +1086,10 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -2201,10 +1100,10 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -2215,10 +1114,10 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -2229,10 +1128,10 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -2243,10 +1142,10 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -2257,10 +1156,10 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -2271,10 +1170,10 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -2285,10 +1184,10 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -2299,10 +1198,10 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -2313,10 +1212,10 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -2327,1230 +1226,1230 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="8" t="s">
+      <c r="B101" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B65" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B87" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B88" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B92" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B93" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B96" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B97" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B100" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>7</v>
-      </c>
       <c r="C101" s="3" t="s">
         <v>5</v>
       </c>
@@ -3558,8 +2457,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A102" s="5"/>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="9"/>
       <c r="B102" s="3"/>
     </row>
     <row r="103" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
